--- a/UAC234-JX-A0_PRD.xlsx
+++ b/UAC234-JX-A0_PRD.xlsx
@@ -18535,7 +18535,7 @@
         <x:v>Beany Beta 初始动作行为查表TA 20260806.xlsx</x:v>
       </x:c>
       <x:c r="B28" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/Beany Beta 初始动作行为查表TA 20260806.xlsx</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/Beany Beta 初始动作行为查表TA 20260806.xlsx</x:v>
       </x:c>
       <x:c r="C28" s="15" t="str">
         <x:v>e28be5be98fed6d3c00cd7081db8f556827aa56f020daed7d8bba62206d2f5eb</x:v>
@@ -18546,7 +18546,7 @@
         <x:v>八个IMU事件触发标准.md</x:v>
       </x:c>
       <x:c r="B29" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/八个IMU事件触发标准.md</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/八个IMU事件触发标准.md</x:v>
       </x:c>
       <x:c r="C29" s="20" t="str">
         <x:v>5c702dc955f0bfc62dab690c7489add9f8e46666c31d089e05b4125ac78fb102</x:v>
@@ -18557,7 +18557,7 @@
         <x:v>其他描述.txt</x:v>
       </x:c>
       <x:c r="B30" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/其他描述.txt</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/其他描述.txt</x:v>
       </x:c>
       <x:c r="C30" s="15" t="str">
         <x:v>d16c5a76df52bf2e591a32e75e62c9b1b7284cf7fa3024e572f0798b7259bf64</x:v>
@@ -18568,7 +18568,7 @@
         <x:v>beany_emotion_machine.pdf</x:v>
       </x:c>
       <x:c r="B31" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/情绪算法/beany_emotion_machine.pdf</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/情绪算法/beany_emotion_machine.pdf</x:v>
       </x:c>
       <x:c r="C31" s="20" t="str">
         <x:v>6998f9d4787151581086c0b3322c17c3d3b54e41de9e741b18e1163f0498b22b</x:v>
@@ -18579,7 +18579,7 @@
         <x:v>daily_emotion_liunian.py</x:v>
       </x:c>
       <x:c r="B32" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/情绪算法/daily_emotion_liunian.py</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/情绪算法/daily_emotion_liunian.py</x:v>
       </x:c>
       <x:c r="C32" s="15" t="str">
         <x:v>a2d90d70501992aca93d732b07f58214541781a82e1aaaad8c39ef3819255fae</x:v>
@@ -18590,7 +18590,7 @@
         <x:v>舵机动作统计表格 20260723 合并版本update_sound update 0901.xlsm</x:v>
       </x:c>
       <x:c r="B33" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/舵机动作统计表格 20260723 合并版本update_sound update 0901.xlsm</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/舵机动作统计表格 20260723 合并版本update_sound update 0901.xlsm</x:v>
       </x:c>
       <x:c r="C33" s="20" t="str">
         <x:v>bcaba8601cc98133ce803245431e084330bb9973fb36455c40afbe688cdf94fa</x:v>
@@ -18601,7 +18601,7 @@
         <x:v>舵机控制板协议_V1.4_20260818.docx</x:v>
       </x:c>
       <x:c r="B34" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/舵机控制板协议_V1.4_20260818.docx</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/舵机控制板协议_V1.4_20260818.docx</x:v>
       </x:c>
       <x:c r="C34" s="15" t="str">
         <x:v>8284639246dc02646aeef7e5b75e0036c055694ae85628ba25fb16b421bb48a0</x:v>
@@ -18612,7 +18612,7 @@
         <x:v>设备功能说明.md</x:v>
       </x:c>
       <x:c r="B35" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/设备功能说明.md</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/设备功能说明.md</x:v>
       </x:c>
       <x:c r="C35" s="20" t="str">
         <x:v>551a9f00bebaae1bd49397702233f026e952e3466e77692768f12078c6a8e891</x:v>
@@ -18623,7 +18623,7 @@
         <x:v>通用BLE协议_V1_0_12.md</x:v>
       </x:c>
       <x:c r="B36" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/UAC234-DJ-A0-TINON-产品资料/通用BLE协议_V1_0_12.md</x:v>
+        <x:v>项目资料/UAC234-DJ-A0-TINON-产品资料/通用BLE协议_V1_0_12.md</x:v>
       </x:c>
       <x:c r="C36" s="15" t="str">
         <x:v>44fd7f67a09fec9fc5feab44741d1cbdca3d39be927eb1f6502ee9ada4bc8fdd</x:v>
@@ -18634,7 +18634,7 @@
         <x:v>UAC234-A0-V1.2.pdf</x:v>
       </x:c>
       <x:c r="B37" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/硬件需求/UAC234-A0-V1.2.pdf</x:v>
+        <x:v>项目资料/PRD/硬件需求/UAC234-A0-V1.2.pdf</x:v>
       </x:c>
       <x:c r="C37" s="20" t="str">
         <x:v>02058ecb35bc5bc6afd6cbc590ce032b85c420e9947637ce8a538ac268a923de</x:v>
@@ -18645,7 +18645,7 @@
         <x:v>IMG_1298.PNG</x:v>
       </x:c>
       <x:c r="B38" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1298.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1298.PNG</x:v>
       </x:c>
       <x:c r="C38" s="15" t="str">
         <x:v>40f8f8c86be2bbb51387a62e4cb31992eff1dd4db069c22cbff01201523ed286</x:v>
@@ -18656,7 +18656,7 @@
         <x:v>IMG_1299.PNG</x:v>
       </x:c>
       <x:c r="B39" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1299.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1299.PNG</x:v>
       </x:c>
       <x:c r="C39" s="20" t="str">
         <x:v>379a8d62c9020b558ce317a974cfffcd4133ae269d8ca378756d5665045ef991</x:v>
@@ -18667,7 +18667,7 @@
         <x:v>IMG_1300.PNG</x:v>
       </x:c>
       <x:c r="B40" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1300.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1300.PNG</x:v>
       </x:c>
       <x:c r="C40" s="15" t="str">
         <x:v>b749a09054155cdce51975fca222419eecb2af38abbe480c0fc934345ed1849d</x:v>
@@ -18678,7 +18678,7 @@
         <x:v>IMG_1301.PNG</x:v>
       </x:c>
       <x:c r="B41" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1301.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1301.PNG</x:v>
       </x:c>
       <x:c r="C41" s="20" t="str">
         <x:v>20a30bd5459c99033f5c001e2145dddee1f14da4e8a6cb793b47f975b3428784</x:v>
@@ -18689,7 +18689,7 @@
         <x:v>IMG_1302.PNG</x:v>
       </x:c>
       <x:c r="B42" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1302.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1302.PNG</x:v>
       </x:c>
       <x:c r="C42" s="15" t="str">
         <x:v>4ab463bd76f3977e5597c4818c71d1dfba3f4a10b04c7ecf8ff26a64c50bbf80</x:v>
@@ -18700,7 +18700,7 @@
         <x:v>IMG_1303.PNG</x:v>
       </x:c>
       <x:c r="B43" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1303.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1303.PNG</x:v>
       </x:c>
       <x:c r="C43" s="20" t="str">
         <x:v>68729936fd055c20986a1f08e9055e371a343f01a82eca3b0e02e3063a095433</x:v>
@@ -18711,7 +18711,7 @@
         <x:v>IMG_1304.PNG</x:v>
       </x:c>
       <x:c r="B44" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1304.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1304.PNG</x:v>
       </x:c>
       <x:c r="C44" s="15" t="str">
         <x:v>5077f02c74ebbcce36e92a7ced0f6616c0b0e2a2f5d8a85db089416bf28001a5</x:v>
@@ -18722,7 +18722,7 @@
         <x:v>IMG_1305.PNG</x:v>
       </x:c>
       <x:c r="B45" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1305.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1305.PNG</x:v>
       </x:c>
       <x:c r="C45" s="20" t="str">
         <x:v>53ab9b858a4a0a5c7721f21e83a396fa08df0418bd7066c0f59e7ed659f1aef0</x:v>
@@ -18733,7 +18733,7 @@
         <x:v>IMG_1306.PNG</x:v>
       </x:c>
       <x:c r="B46" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1306.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1306.PNG</x:v>
       </x:c>
       <x:c r="C46" s="15" t="str">
         <x:v>84e73255194ba3ca882a55dfd4173307f226aac23bf61e1fa8dc36dfa45e3d02</x:v>
@@ -18744,7 +18744,7 @@
         <x:v>IMG_1307.PNG</x:v>
       </x:c>
       <x:c r="B47" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1307.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1307.PNG</x:v>
       </x:c>
       <x:c r="C47" s="20" t="str">
         <x:v>283f997cfce2ac0632f36945a118c68b0dc51d09dc900c20542a6326091c97bd</x:v>
@@ -18755,7 +18755,7 @@
         <x:v>IMG_1308.PNG</x:v>
       </x:c>
       <x:c r="B48" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1308.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1308.PNG</x:v>
       </x:c>
       <x:c r="C48" s="15" t="str">
         <x:v>badefad24913710f1a4f05e1fd325f184623566a3c09a20b7b1ba26318ee46dc</x:v>
@@ -18766,7 +18766,7 @@
         <x:v>IMG_1311.PNG</x:v>
       </x:c>
       <x:c r="B49" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1311.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1311.PNG</x:v>
       </x:c>
       <x:c r="C49" s="20" t="str">
         <x:v>5621c01a61a3af33fe19a44e76081a068a28739b6d48b55f059d8ccb75d23203</x:v>
@@ -18777,7 +18777,7 @@
         <x:v>IMG_1312.PNG</x:v>
       </x:c>
       <x:c r="B50" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1312.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1312.PNG</x:v>
       </x:c>
       <x:c r="C50" s="15" t="str">
         <x:v>c056ea0eef74ad1786aa68be29617b3d8839a351c5f80d1125b5a1e48a63178a</x:v>
@@ -18788,7 +18788,7 @@
         <x:v>IMG_1313.PNG</x:v>
       </x:c>
       <x:c r="B51" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1313.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1313.PNG</x:v>
       </x:c>
       <x:c r="C51" s="20" t="str">
         <x:v>c48a0ec31dda7c450f9c0477eceec049f5272377cc416d1ea0f330fbe012e24f</x:v>
@@ -18799,7 +18799,7 @@
         <x:v>IMG_1317.PNG</x:v>
       </x:c>
       <x:c r="B52" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1317.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1317.PNG</x:v>
       </x:c>
       <x:c r="C52" s="15" t="str">
         <x:v>5eabcb1f87f1a6a3cb98078fd2ab3439c541151296e72353279844e4b7dca457</x:v>
@@ -18810,7 +18810,7 @@
         <x:v>IMG_1319.PNG</x:v>
       </x:c>
       <x:c r="B53" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1319.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1319.PNG</x:v>
       </x:c>
       <x:c r="C53" s="20" t="str">
         <x:v>6d846f99f8c19d07d2820139b192466e61f15a7d9eb4967ee710667a4c6a622b</x:v>
@@ -18821,7 +18821,7 @@
         <x:v>IMG_1320.PNG</x:v>
       </x:c>
       <x:c r="B54" s="15" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1320.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1320.PNG</x:v>
       </x:c>
       <x:c r="C54" s="15" t="str">
         <x:v>b8865fa0e85029e2a1d927bbbab2e69cd48467ed9f2fb2d3c4304d8330af4c54</x:v>
@@ -18832,7 +18832,7 @@
         <x:v>IMG_1322.PNG</x:v>
       </x:c>
       <x:c r="B55" s="20" t="str">
-        <x:v>/Users/haywardlin/haywardws/产品需求/内部项目/UAC234-JX-A0（舵机控制）/PRD/APP需求/IMG_1322.PNG</x:v>
+        <x:v>项目资料/PRD/APP需求/IMG_1322.PNG</x:v>
       </x:c>
       <x:c r="C55" s="20" t="str">
         <x:v>a605fdd5a2db8c95ae3ccff525d28e3d5a5fe6ead0c87eb21ab3990edf3160fc</x:v>

--- a/UAC234-JX-A0_PRD.xlsx
+++ b/UAC234-JX-A0_PRD.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品概述" sheetId="1" r:id="Rf6dce0e6aaf949e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬件需求" sheetId="2" r:id="R669d67dade75469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固件需求" sheetId="3" r:id="R83351d0b2f5e49e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP协议" sheetId="4" r:id="Rfa7b2acff05a46b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP页面体验" sheetId="5" r:id="R8ae1c8feaee64638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情绪算法" sheetId="6" r:id="Re7832b105a584818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成长与更新" sheetId="7" r:id="R4fd2b211f13d4094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初识" sheetId="8" r:id="R13adc1f6ecdb4249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="熟悉" sheetId="9" r:id="R1b0637e258af4989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相伴" sheetId="10" r:id="Ra60089795705486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑与故事" sheetId="11" r:id="Rc4bfdade872241a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自定义动作" sheetId="12" r:id="R20ffab06dca3434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互矩阵" sheetId="13" r:id="R7ddf5f9672ed4cf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态与流程" sheetId="14" r:id="Rcc9d05baafd5489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源映射" sheetId="15" r:id="R36f4611e01e24a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料与待补" sheetId="16" r:id="R2328280d97c543f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品概述" sheetId="1" r:id="Rd52d9ec5aacf4648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬件需求" sheetId="2" r:id="R7f2d1e3c0f784bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固件需求" sheetId="3" r:id="R66364056000e4b4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP协议" sheetId="4" r:id="R1e9fbcd5dac942e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APP页面体验" sheetId="5" r:id="Re1a22b7d8da64b8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="情绪算法" sheetId="6" r:id="R1e405a6bd569455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成长与更新" sheetId="7" r:id="R0b5a87080b4142d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初识" sheetId="8" r:id="Rbd5274f7fc444abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="熟悉" sheetId="9" r:id="R37386313906f4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相伴" sheetId="10" r:id="R2dd765dd6b1b42b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑与故事" sheetId="11" r:id="R1c08c487ff51417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自定义动作" sheetId="12" r:id="Reb94ac4a883d4516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交互矩阵" sheetId="13" r:id="Rfa11deee84994c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态与流程" sheetId="14" r:id="R6c16efcd03414e8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源映射" sheetId="15" r:id="R23bfc2882c6b4acd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资料与待补" sheetId="16" r:id="R525161c1290b4b98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -455,12 +455,12 @@
         <x:v>需求定义</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+    <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="15" t="str">
         <x:v>产品定位</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>通过触摸、姿态、光感和固定唤醒词互动的陪伴玩具，以动作、伴音和震动表达反馈；App负责设置、养成与动作编排。</x:v>
+        <x:v>通过触摸、姿态、光感和固定唤醒词互动的陪伴玩具，以动作、伴音和震动表达反馈；App负责设置、养成与动作步骤2。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -8896,7 +8896,7 @@
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>使用已验证动作卡片编排；保存、预览和绑定分开确认。绑定后覆盖该事件的系统随机反馈。</x:v>
+        <x:v>一规则一输入；基础动作按步骤与次数执行。保存为App本机草稿，启用需完整校验、下发和读回。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -8910,183 +8910,183 @@
       </x:c>
       <x:c r="C5" s="10"/>
     </x:row>
-    <x:row r="6" ht="34" customHeight="1">
+    <x:row r="6" ht="44" customHeight="1">
       <x:c r="A6" s="15" t="str">
         <x:v>功能范围</x:v>
       </x:c>
       <x:c r="B6" s="22" t="str">
-        <x:v>首版使用现有动作ID卡片编排，不开放任意舵机角度、速度、限位或未验证关键帧。每张卡由已验证动作、可选配套音频及震动配置组成。</x:v>
+        <x:v>一条规则只选一个输入事件，按顺序执行多个动作步骤；每步设置基础动作和重复次数。默认示例：左右摇头5次→上下点头2次，共2步、7个动作循环。四类输入均可编辑草稿；不开放自由角度、速度和关键帧。</x:v>
       </x:c>
       <x:c r="C6" s="22"/>
     </x:row>
-    <x:row r="7" ht="34" customHeight="1">
+    <x:row r="7" ht="44" customHeight="1">
       <x:c r="A7" s="20" t="str">
         <x:v>初始模式可用</x:v>
       </x:c>
       <x:c r="B7" s="20" t="str">
-        <x:v>App可在初始模式保存、预览和独立绑定自定义动作；绑定不启用成长，界面显示“初始模式·有自定义绑定”。从未App更新的设备仍完整执行原始行为表。</x:v>
+        <x:v>初始模式可保存本机草稿；设备支持并完成启用核对后可执行用户规则。启用动作规则不启用五行或成长。从未更新且无已启用规则的设备继续使用原始行为表。</x:v>
       </x:c>
       <x:c r="C7" s="20"/>
     </x:row>
-    <x:row r="8" ht="34" customHeight="1">
+    <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="15" t="str">
         <x:v>数量与名称</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>每设备最多8条已保存自定义作品；名称1–12个可见字符。草稿不占设备槽位；资源确认占位，删除清理成功才释放。名称为空或超限不能保存。</x:v>
+        <x:v>每设备最多8条已启用规则；名称1–12个可见字符。App本机草稿不占启用名额。一个输入最多1条启用规则，一条规则只对应一个输入。停用确认后释放启用名额；结果未知先核对，资源清理状态独立显示。</x:v>
       </x:c>
       <x:c r="C8" s="15"/>
     </x:row>
-    <x:row r="9" ht="34" customHeight="1">
+    <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="20" t="str">
-        <x:v>卡片与顺序</x:v>
-      </x:c>
-      <x:c r="B9" s="20" t="str">
-        <x:v>每条1–3张卡，可添加、删除和上下换序；卡间停顿仅0/0.5/1秒，最后一张不另计停顿。卡片原生速度与幅度不向用户开放。</x:v>
+        <x:v>步骤与次数</x:v>
+      </x:c>
+      <x:c r="B9" s="21" t="str">
+        <x:v>本次设计建议：每条1–10步，每步1–10次整数；需研发确认存储容量与驱动能力，正式范围以设备能力为准。可新增、删除、上下重排步骤。步间停顿可选0／0.5／1秒，最后一步不计停顿。</x:v>
       </x:c>
       <x:c r="C9" s="20"/>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="15" t="str">
         <x:v>时长校验</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
-        <x:v>整条总时长≤5秒。单卡时长由已验证资源清单提供，为该卡动作、音频和震动实际播放跨度的最大值；若卡内错峰则按最后结束时间计算。总时长为各卡时长加卡间停顿。缺时长或单卡已超5秒的资源不进入可用卡库。</x:v>
+      <x:c r="B10" s="22" t="str">
+        <x:v>每步时长=max（单周期时长×次数，音频跨度，震动跨度）；总时长=各步时长之和＋步间停顿。声音、震动关闭时跨度为0。周期或跨度未知标“待标定”，可存草稿，禁止真机预览和启用。总时长上限由设备安全能力配置；本轮不虚设秒数。源普通反馈最长5秒机制保留，多步序列另行调度。</x:v>
       </x:c>
       <x:c r="C10" s="15"/>
     </x:row>
-    <x:row r="11" ht="48" customHeight="1">
+    <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:v>音频</x:v>
       </x:c>
       <x:c r="B11" s="20" t="str">
-        <x:v>用户可选静音逻辑ID=0或该动作已经验证的配套音频ID；不能任意拼接目录外文件。现有音频资源ID按目录1–61引用，文件名与实际文件须经资源包核对。静音不改变动作轨迹，也不隐去系统提示。</x:v>
+        <x:v>新步骤默认关闭音频；可选该基础动作已经验证的配套音频。每步开始播放1次，不随动作次数倍增；下一步等待动作循环与音频、震动全部完成。音频1–61仅是原目录，未验证与基础动作配对的不能开放；唤醒必要提示先执行，不能被关闭。</x:v>
       </x:c>
       <x:c r="C11" s="20"/>
     </x:row>
-    <x:row r="12" ht="48" customHeight="1">
+    <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="15" t="str">
         <x:v>震动</x:v>
       </x:c>
       <x:c r="B12" s="22" t="str">
-        <x:v>App逻辑ID统一0=关闭、1=弱、2=中、3=强；仅显示该卡已验证的档位，默认沿用卡片配置，可关闭。原表只定义1/2/3强度名称；0为本次无震动约定。实际PWM/时长及停止能力须联调，未验证不开放对应档位。</x:v>
+        <x:v>新步骤默认关闭震动。逻辑值0=关闭、1=弱、2=中、3=强，仅开放已验证搭配。每步开始播放1次，不随动作次数倍增；强度、跨度和停止能力需验证，原表强弱名称不等于驱动参数已经齐全。</x:v>
       </x:c>
       <x:c r="C12" s="22"/>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
+    <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="20" t="str">
         <x:v>ID编码转换</x:v>
       </x:c>
       <x:c r="B13" s="20" t="str">
-        <x:v>动作、音频、震动与情绪是独立ID空间。App静音/无震动逻辑0写入源7字节行为表时转换为0xFF“不播放”；序列协议需约定同一语义。行为表情绪ID仅0 ANY、1开心、2平静、3悲伤，不新增子情绪ID。</x:v>
+        <x:v>事件ID保持原义；动作、音频、震动与情绪为独立ID空间。原7字节行为表的音频/震动“不播放”为0xFF，App逻辑0需转换；新序列协议须明确对应语义。情绪仍为0 ANY、1开心、2平静、3悲伤。不得把动作重复次数写入事件count。</x:v>
       </x:c>
       <x:c r="C13" s="20"/>
     </x:row>
-    <x:row r="14" ht="34" customHeight="1">
+    <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>资源映射</x:v>
-      </x:c>
-      <x:c r="B14" s="15" t="str">
-        <x:v>逻辑动作ID先查已验证的控制板映射；0x03的载荷是预置索引，不等于动作ID。动作/音频/震动作为一张卡整体绑定版本和校验值；命令接收成功不代表动作完成。</x:v>
+        <x:v>基础动作映射</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:v>左右摇头一次：中→左→右→中；上下点头一次：中→上→下→中。真实资源ID、轴对应、零位、安全角度、速度、周期时长与完成回执待标定。不得把复合情绪动作13当作单次点头：原13本身为连续点头3次。原12、57、59也未验证为本次单周期基础动作。</x:v>
       </x:c>
       <x:c r="C14" s="15"/>
     </x:row>
-    <x:row r="15" ht="48" customHeight="1">
+    <x:row r="15" ht="44" customHeight="1">
       <x:c r="A15" s="20" t="str">
         <x:v>预览</x:v>
       </x:c>
       <x:c r="B15" s="20" t="str">
-        <x:v>连接且鉴权通过后校验当前状态和完整资源，预览整个序列。预览来源标为App测试，不写真实互动成长、里程碑或故事。暗环境、深度睡眠、充电等禁止输出状态拒绝预览；浅睡须先由新增调度唤醒必要模块。</x:v>
+        <x:v>草稿可离线保存；真机预览须连接、鉴权、资源完整、时长与安全能力已确认。预览整条一次并显示当前步/次数，提供停止；预览不计成长、里程碑或故事。暗环境、深睡、充电、静默、睡眠时段及升级/更新中不预览。浅睡调度须另行实现，未知任务结果先查询。</x:v>
       </x:c>
       <x:c r="C15" s="20"/>
     </x:row>
-    <x:row r="16" ht="48" customHeight="1">
+    <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="15" t="str">
         <x:v>优先级与停止</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>预览和触摸自定义动作按触摸级调度；系统、交友、IMU可打断。用户停止或保护触发后取消剩余卡片；等待停止/完成确认才释放任务，断连不假定已停。结束后恢复无互动计时，不改变原睡眠门槛。</x:v>
+        <x:v>真实事件沿用原事件优先级，唤醒28先完成必要提示；预览按触摸级。系统＞交友＞姿态＞触摸＞光感，高优先级或保护打断，同级/低级丢弃、不排队。停止取消剩余循环和步骤，不续播；收到停止/完成确认才释放任务，断连不当作已停止。</x:v>
       </x:c>
       <x:c r="C16" s="15"/>
     </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+    <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="20" t="str">
-        <x:v>保存不是绑定</x:v>
+        <x:v>保存与启用</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
-        <x:v>先把新资源版本保存到设备并核对成功，再开放绑定。列表分别显示草稿、资源已保存、绑定待同步、已绑定、结果待确认、待清理。编辑已绑定作品先存新版本，原版本持续生效到新配置确认完成。</x:v>
+        <x:v>“保存草稿”须具备一个允许输入、有效名称、至少一步及合法整数次数，仅存App本机；不要求在线或真实ID/时长已标定。未填完是未保存编辑，不提示永久保存成功。“启用”须校验完整能力/资源后传输、原子提交并读回一致。编辑已启用规则或切换输入确认前旧版继续生效；结果不明先查询。</x:v>
       </x:c>
       <x:c r="C17" s="21"/>
     </x:row>
-    <x:row r="18" ht="34" customHeight="1">
+    <x:row r="18" ht="44" customHeight="1">
       <x:c r="A18" s="15" t="str">
-        <x:v>绑定输入</x:v>
+        <x:v>输入事件</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>首版仅普通轻触事件1/4/7/10/13/16/19可绑定；每个输入最多1条用户序列，同一作品可绑定多个允许输入。替换已绑定输入时明确提示被替换作品，不静默删除。</x:v>
+        <x:v>触摸：1头顶、4头左、7头右、10腹部、13身体左、16身体右、19后背；唤醒：28；光感：30变亮；IMU：23轻摇。触摸/28/30原Beta=Y；23原Beta=N，本轮新增实现，实机确认支持后才可启用。四类均可选为草稿输入。保护/自动系统/变暗24、29、31、32、35–42不开放；其余未列入输入也不开放。</x:v>
       </x:c>
       <x:c r="C18" s="15"/>
     </x:row>
-    <x:row r="19" ht="48" customHeight="1">
+    <x:row r="19" ht="44" customHeight="1">
       <x:c r="A19" s="20" t="str">
-        <x:v>绑定后概率</x:v>
+        <x:v>启用后输出</x:v>
       </x:c>
       <x:c r="B19" s="20" t="str">
-        <x:v>在允许输出的状态下，已绑定输入100%执行对应用户序列，按卡片顺序播放，不再抽取该事件的成长候选，也不叠加性格倍率。安全屏蔽、优先级与互斥先判断；被屏蔽时仍不执行。未绑定输入继续按生效阶段→事件→情绪组ID→权重抽整套输出。</x:v>
+        <x:v>在状态、资源、优先级均允许时，命中已启用规则后整条只运行一遍；该输入不再抽成长反馈，也不叠加性格倍率。每步全部次数完成后再执行下一步。未启用输入沿用当前阶段默认反馈；同输入已有规则时明确显示被替换规则并确认。</x:v>
       </x:c>
       <x:c r="C19" s="20"/>
     </x:row>
-    <x:row r="20" ht="48" customHeight="1">
+    <x:row r="20" ht="44" customHeight="1">
       <x:c r="A20" s="15" t="str">
-        <x:v>真人触摸仍成长</x:v>
+        <x:v>真实输入与成长</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>真人触发绑定输入时，设备记录原事件ID和正常有效count；养成已启用后按该输入正常计五维和XP，输出内容不同不改变积分。初始模式只留普通事件，不因此启用或追溯增长；App预览始终不计。</x:v>
+        <x:v>一次真实有效输入按原事件记录一次；默认示例7个输出循环不等于7次互动。启用成长后，获准触摸/唤醒及已验收轻摇按原规则计分；变亮30和预览不计XP。初始模式不启用或追溯成长。动作完成回执不产生新的用户事件记录。</x:v>
       </x:c>
       <x:c r="C20" s="15"/>
     </x:row>
-    <x:row r="21" ht="48" customHeight="1">
+    <x:row r="21" ht="44" customHeight="1">
       <x:c r="A21" s="20" t="str">
-        <x:v>成长包保留绑定</x:v>
+        <x:v>成长包保留规则</x:v>
       </x:c>
       <x:c r="B21" s="20" t="str">
-        <x:v>用户作品与绑定层独立保存。App生成新阶段基础规则后叠加全部已确认用户绑定，完整核验资源与绑定版本再提交。正常阶段更新、回滚成长基础包或重启不得清空用户作品/绑定。资源冲突则拒绝该新包，不静默降级或删除绑定。</x:v>
+        <x:v>用户规则与成长基础表独立保存。更新阶段或回滚基础包时保留当前已确认规则版本、输入和启用状态；冲突拒绝提交，不静默删除。原触发ID和原始成长向量不因输出步骤改变。</x:v>
       </x:c>
       <x:c r="C21" s="20"/>
     </x:row>
-    <x:row r="22" ht="48" customHeight="1">
+    <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="15" t="str">
-        <x:v>保存/绑定失败</x:v>
+        <x:v>启用失败</x:v>
       </x:c>
       <x:c r="B22" s="22" t="str">
-        <x:v>资源传输失败保留App草稿，已生效作品不变；新资源已存但绑定未成功，不显示已绑定。提交后回执丢失显示结果待确认，读回绑定版本和资源状态后再重试，不能直接宣称旧配置已恢复。</x:v>
+        <x:v>提交前校验或传输失败保留草稿及旧生效版；提交后回执丢失显示结果待确认，读取实际版本后恢复。不得显示未经读回的已启用。编辑或切换输入失败不得先解除旧规则；设备须补全原子替换能力。</x:v>
       </x:c>
       <x:c r="C22" s="22"/>
     </x:row>
-    <x:row r="23" ht="48" customHeight="1">
+    <x:row r="23" ht="44" customHeight="1">
       <x:c r="A23" s="20" t="str">
-        <x:v>删除与解绑</x:v>
+        <x:v>停用与删除</x:v>
       </x:c>
       <x:c r="B23" s="20" t="str">
-        <x:v>取消绑定只解除选定输入，恢复当前生效基础表对该输入的默认反馈，作品、成长、里程碑和故事保留。删除作品必须先解绑所有引用并核对，再删除资源；解绑失败不删，解绑成功但清理失败显示未绑定/待清理。</x:v>
+        <x:v>停用后读回确认，恢复该输入当前基础反馈，草稿保留并释放启用名额。删除已启用规则须先停用并确认，再清设备资源；停用失败不删，清理失败单独显示待清理，不恢复启用占用。纯本机草稿可离线删除。成长、里程碑、故事不随作品删除。</x:v>
       </x:c>
       <x:c r="C23" s="20"/>
     </x:row>
-    <x:row r="24" ht="34" customHeight="1">
+    <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="15" t="str">
-        <x:v>多卡互斥</x:v>
+        <x:v>执行与IMU互锁</x:v>
       </x:c>
       <x:c r="B24" s="15" t="str">
-        <x:v>整个序列视为一个任务；前一张卡片音频结束不代表整条结束。每卡按声明的播放跨度完成后再等待间隔、进入下一卡；任何一段失败均停止余下卡片并返回明确结果。</x:v>
+        <x:v>整个序列为一个任务；每步等待所有循环及可选声音/震动完成后进入停顿和下一步。任何步骤失败或被打断都取消余下，不自动重播。屏蔽舵机自身运动引起的普通IMU反触发，保护检测始终保留；屏蔽窗口和恢复条件需实机验证。光感不重置互动计时，浅睡约6秒短唤醒需验证与序列总时长协调。</x:v>
       </x:c>
       <x:c r="C24" s="15"/>
     </x:row>
-    <x:row r="25" ht="48" customHeight="1">
+    <x:row r="25" ht="44" customHeight="1">
       <x:c r="A25" s="20" t="str">
         <x:v>接口范围</x:v>
       </x:c>
       <x:c r="B25" s="20" t="str">
-        <x:v>序列保存/查询、预览/停止、完成/中止、绑定/解绑/版本回读、资源校验与事务结果是新增产品接口要求，源App协议尚未完整提供。0x51仅舵机MCU升级透传，不当作普通App动作业务控制。</x:v>
+        <x:v>新增能力：事件支持查询、基础动作能力/时长、安全总时长、完整规则保存/查询/原子启用/停用、按步按次调度、任务完成/停止/中止回执及IMU自触发抑制。原0x03只确认收命令，0x04未定义顺序/次数，0x05缺标定和完整App入口，0x51仅MCU OTA透传；不能串发0x03冒充完成闭环。</x:v>
       </x:c>
       <x:c r="C25" s="20"/>
     </x:row>
@@ -9115,21 +9115,21 @@
       </x:c>
       <x:c r="C30" s="15"/>
     </x:row>
-    <x:row r="31" ht="34" customHeight="1">
+    <x:row r="31" ht="44" customHeight="1">
       <x:c r="A31" s="20" t="str">
-        <x:v>删除自定义作品</x:v>
+        <x:v>删除自定义可编辑输入</x:v>
       </x:c>
       <x:c r="B31" s="20" t="str">
-        <x:v>先解绑所有引用，再删除设备资源和作品记录。 不变；只删除该作品；里程碑/故事保留；解绑失败不删；清理失败显示待清理</x:v>
+        <x:v>已启用规则先停用并确认，再清设备资源；纯本机草稿可离线删除。 不变；只删除该作品；里程碑/故事保留；停用失败不删；停用确认释放启用名额，清理状态独立</x:v>
       </x:c>
       <x:c r="C31" s="20"/>
     </x:row>
-    <x:row r="32" ht="48" customHeight="1">
+    <x:row r="32" ht="44" customHeight="1">
       <x:c r="A32" s="15" t="str">
         <x:v>重新开始养成（含恢复初始）</x:v>
       </x:c>
       <x:c r="B32" s="15" t="str">
-        <x:v>二次确认后，恢复原始行为表，清当前成长摘要/台账、里程碑/故事和全部用户触摸绑定。不另设全局“恢复初始互动模式”入口。 回到初始模式；下次启用从0 XP开始；清当前档案成长记录；用户作品可保留为未绑定草稿；新增重置养成接口，必须二次确认，不冒充恢复出厂</x:v>
+        <x:v>二次确认后，恢复原始行为表，清当前成长摘要/台账、里程碑/故事和全部用户输入规则。不另设全局“恢复初始互动模式”入口。 回到初始模式；下次启用从0 XP开始；清当前档案成长记录；用户作品可保留为未绑定草稿；新增重置养成接口，必须二次确认，不冒充恢复出厂</x:v>
       </x:c>
       <x:c r="C32" s="15"/>
     </x:row>
@@ -9191,48 +9191,48 @@
         <x:v>原0x44两侧独立提交，不具备整包原子语义；新增字段/读回要求。</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="48" customHeight="1">
+    <x:row r="41" ht="60" customHeight="1">
       <x:c r="A41" s="15" t="str">
         <x:v>序列资源与时长</x:v>
       </x:c>
       <x:c r="B41" s="15" t="str">
-        <x:v>每张卡的实际动作/音频/震动跨度、兼容固件、控制映射、校验值和停止能力；能保存1–3卡用户序列并查询版本。</x:v>
+        <x:v>新增摇头一次/点头一次的真实ID、轴与零位、安全范围、周期、结束回执；规则含一个输入和有序步骤/次数。回读固件支持事件、正式步数/次数及安全总时长上限；完整规则按版本校验。</x:v>
       </x:c>
       <x:c r="C41" s="15" t="str">
-        <x:v>现有资源表为逻辑定义，没有完整卡片实物、实际时长与组合协议。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="34" customHeight="1">
+        <x:v>源13为连续点头3次；12/57/59未验证为本次单周期动作。原0x03只收令应答，0x04未定义串行/重复语义，0x05仍缺标定/字节序核对与App入口。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="60" customHeight="1">
       <x:c r="A42" s="20" t="str">
         <x:v>普通App预览控制</x:v>
       </x:c>
       <x:c r="B42" s="20" t="str">
-        <x:v>预览/停止、执行中/完成/中止/失败结果、明确任务ID；输入来源标记避免预览被计成长。</x:v>
-      </x:c>
-      <x:c r="C42" s="20" t="str">
-        <x:v>现协议无完整预览业务；0x51为MCU OTA透传，不能直接替代。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="48" customHeight="1">
+        <x:v>独立序列调度：任务ID、步骤进度、循环完成、整条完成/停止/中止/失败；停止取消余下。每步音频/震动各1次，全部结束才换步；禁止以串发0x03代替完成确认。</x:v>
+      </x:c>
+      <x:c r="C42" s="21" t="str">
+        <x:v>原普通反馈5秒机制继续有效；序列安全总时长与浅睡约6秒短唤醒协调待实现。0x51仅OTA透传；实际序列能力尚未验证。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="44" customHeight="1">
       <x:c r="A43" s="15" t="str">
         <x:v>震动档位</x:v>
       </x:c>
       <x:c r="B43" s="15" t="str">
-        <x:v>0关闭、1弱、2中、3强的逻辑值到驱动指令/实际时长/停止的映射，按卡校验可用档位。</x:v>
+        <x:v>新步骤音频和震动默认关闭；可选验证配对，开始时各播放1次。0关闭、1弱、2中、3强到驱动/实际跨度/停止的映射按基础动作验证。</x:v>
       </x:c>
       <x:c r="C43" s="15" t="str">
         <x:v>原资源表1–3有名称；控制板Moto命令缺完整强度/时长负载，0关闭为新增约定。</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="48" customHeight="1">
+    <x:row r="44" ht="60" customHeight="1">
       <x:c r="A44" s="20" t="str">
         <x:v>独立绑定层</x:v>
       </x:c>
       <x:c r="B44" s="20" t="str">
-        <x:v>按输入查询/替换/解除绑定，保存绑定版本；成长基础表更新后100%用户序列仍覆盖对应输入。</x:v>
+        <x:v>一规则一输入，一输入一启用规则，最多8条已启用；完整传输后原子启用或替换输入，读回内容/版本；失败保留旧规则。轻摇23源Beta N须新增验收。屏蔽舵机自运动的普通IMU反触发，保护不中断检测。</x:v>
       </x:c>
       <x:c r="C44" s="20" t="str">
-        <x:v>现有7字节规则只有单个输出ID，不能自然表达多卡序列与独立绑定层，需扩展调度和存储。</x:v>
+        <x:v>源7字节规则只有单输出ID，不能直接表示有序步骤/次数；规则存储、事务替换、能力查询、IMU互锁和停止完成需新增。</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="48" customHeight="1">
@@ -9300,21 +9300,21 @@
       </x:c>
       <x:c r="C53" s="15"/>
     </x:row>
-    <x:row r="54" ht="48" customHeight="1">
+    <x:row r="54" ht="44" customHeight="1">
       <x:c r="A54" s="20" t="str">
         <x:v>自定义动作与成长共存</x:v>
       </x:c>
       <x:c r="B54" s="20" t="str">
-        <x:v>初始模式保存作品并绑定头顶轻触 → 该输入100%执行用户序列，界面仍是初始模式 → App首次启用成长后，绑定保留 → 真人再次触摸按事件1计成长；App预览不计 → 更新熟悉/相伴包后绑定仍在；取消绑定恢复当前阶段默认概率</x:v>
+        <x:v>初始模式选择触摸1，保存“摇头5次→点头2次”本机草稿 → 能力与资源确认后启用并读回，界面仍为初始模式 → 一次真人触摸只运行整条一次，7个循环不形成7次互动 → 启用成长后一次有效触摸按原事件1计分；光感30与预览无XP → 更新成长包保留规则；停用恢复当前基础反馈</x:v>
       </x:c>
       <x:c r="C54" s="20"/>
     </x:row>
-    <x:row r="55" ht="48" customHeight="1">
+    <x:row r="55" ht="44" customHeight="1">
       <x:c r="A55" s="15" t="str">
         <x:v>故事失败和删除异常</x:v>
       </x:c>
       <x:c r="B55" s="15" t="str">
-        <x:v>里程碑达成时正文生成失败，保留唯一故事占位 → 重试同一实例，按冻结变量生成正文 → 删除绑定作品时先解绑 → 资源清理失败显示未绑定/待清理，不恢复旧绑定 → 重试清理成功后才释放作品槽位</x:v>
+        <x:v>故事正文失败重试同一实例 → 删除已启用规则先停用并核对，成功释放启用名额 → 清理失败显示待清理，不恢复旧绑定和启用占用 → 纯本机草稿可离线删除，不影响成长或故事</x:v>
       </x:c>
       <x:c r="C55" s="15"/>
     </x:row>
@@ -12623,14 +12623,14 @@
         <x:v>步骤</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="116" customHeight="1">
+    <x:row r="6" ht="108" customHeight="1">
       <x:c r="A6" s="15" t="str">
         <x:v>一次互动的输出路径</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
         <x:v>输入识别→事件ID
 检查状态、启用、去重与优先级
-有效自定义绑定：直接执行；否则检查模式
+有效自定义规则：必要提示后逐步执行；否则检查模式
 初始：初始表ANY；成长：生效阶段表＋情绪分组
 按组内权重一次抽取完整候选
 解析动作/伴音/震动资源并执行；高优先级可中断</x:v>
@@ -12674,17 +12674,17 @@
 失败重试同一篇，不重复奖励或生成</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="116" customHeight="1">
+    <x:row r="10" ht="108" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>自定义动作与实际互动</x:v>
+        <x:v>输入事件与有序动作编排</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>选择1–3张已验证卡片并排序
-名称1–12字、停顿0/0.5/1秒、总时长≤5秒
-可预览/停止，预览不记成长
-保存并回读确认作品
-另行绑定普通轻触ID并确认
-真实触摸100%执行用户序列，获准事件记1次成长</x:v>
+        <x:v>一个输入：触摸／轻摇23／唤醒28／变亮30
+左右摇头5次→上下点头2次，共2步、7循环
+保存App本机草稿；事件/资源/时长未知禁止真机启用
+启用：校验→传完整规则→原子提交→读回确认
+真实输入：状态/优先级通过→必要提示→逐步按次数执行
+完成或停止确认后结束；被打断取消余下；原输入记一次，光感与预览无XP</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
@@ -12736,28 +12736,27 @@
 若直接提交≥30XP相伴包，可一次解锁M08和M09，不伪造中间运行</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="99" customHeight="1">
+    <x:row r="18" ht="92" customHeight="1">
       <x:c r="A18" s="20" t="str">
         <x:v>自定义动作与成长共存</x:v>
       </x:c>
       <x:c r="B18" s="20" t="str">
-        <x:v>初始模式保存作品并绑定头顶轻触
-该输入100%执行用户序列，界面仍是初始模式
-App首次启用成长后，绑定保留
-真人再次触摸按事件1计成长；App预览不计
-更新熟悉/相伴包后绑定仍在；取消绑定恢复当前阶段默认概率</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="99" customHeight="1">
+        <x:v>初始模式选择触摸1，保存“摇头5次→点头2次”本机草稿
+能力与资源确认后启用并读回，界面仍为初始模式
+一次真人触摸只运行整条一次，7个循环不形成7次互动
+启用成长后一次有效触摸按原事件1计分；光感30与预览无XP
+更新成长包保留规则；停用恢复当前基础反馈</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="76" customHeight="1">
       <x:c r="A19" s="15" t="str">
         <x:v>故事失败和删除异常</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>里程碑达成时正文生成失败，保留唯一故事占位
-重试同一实例，按冻结变量生成正文
-删除绑定作品时先解绑
-资源清理失败显示未绑定/待清理，不恢复旧绑定
-重试清理成功后才释放作品槽位</x:v>
+        <x:v>故事正文失败重试同一实例
+删除已启用规则先停用并核对，成功释放启用名额
+清理失败显示待清理，不恢复旧绑定和启用占用
+纯本机草稿可离线删除，不影响成长或故事</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12790,7 +12789,7 @@
   <x:sheetData>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>UAC234-JX-A0 资源映射</x:v>
+        <x:v>UAC234-JX-A0 基础动作映射</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -12865,19 +12864,19 @@
       <x:c r="H7" s="20"/>
       <x:c r="I7" s="20"/>
     </x:row>
-    <x:row r="8" ht="34" customHeight="1">
+    <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="15" t="str">
-        <x:v>3 用户绑定</x:v>
+        <x:v>3 用户规则</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>七个普通轻触事件的当前已确认绑定</x:v>
+        <x:v>获准触摸、轻摇23、唤醒28、变亮30的已确认规则</x:v>
       </x:c>
       <x:c r="C8" s="15"/>
       <x:c r="D8" s="15"/>
       <x:c r="E8" s="15"/>
       <x:c r="F8" s="15"/>
       <x:c r="G8" s="15" t="str">
-        <x:v>存在有效绑定时100%执行用户序列；仍按真实输入记成长。</x:v>
+        <x:v>一规则一输入；23须确认支持。唤醒先必要提示；命中后按步骤/次数整条一次。一次真实输入只记一次，光感无XP。</x:v>
       </x:c>
       <x:c r="H8" s="15"/>
       <x:c r="I8" s="15"/>
@@ -12916,36 +12915,36 @@
       <x:c r="H10" s="15"/>
       <x:c r="I10" s="15"/>
     </x:row>
-    <x:row r="11" ht="34" customHeight="1">
+    <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:v>6 资源解析</x:v>
       </x:c>
       <x:c r="B11" s="20" t="str">
-        <x:v>逻辑ID→资源包→控制板命令/播放接口</x:v>
+        <x:v>原逻辑资源与新增单周期基础动作分开</x:v>
       </x:c>
       <x:c r="C11" s="20"/>
       <x:c r="D11" s="20"/>
       <x:c r="E11" s="20"/>
       <x:c r="F11" s="20"/>
-      <x:c r="G11" s="20" t="str">
-        <x:v>动作逻辑ID不等于0x03的控制码。无震动逻辑0编译为0xFF。</x:v>
+      <x:c r="G11" s="21" t="str">
+        <x:v>原逻辑ID不等于0x03控制码；新摇头/点头真实ID、轴/安全范围、周期与完成能力待标定，不套用复合13。</x:v>
       </x:c>
       <x:c r="H11" s="20"/>
       <x:c r="I11" s="20"/>
     </x:row>
-    <x:row r="12" ht="34" customHeight="1">
+    <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="15" t="str">
         <x:v>7 执行与结束</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>完整输出或用户序列</x:v>
+        <x:v>普通反馈或新多步序列调度</x:v>
       </x:c>
       <x:c r="C12" s="15"/>
       <x:c r="D12" s="15"/>
       <x:c r="E12" s="15"/>
       <x:c r="F12" s="15"/>
       <x:c r="G12" s="15" t="str">
-        <x:v>保留原播放与打断规则；自定义序列等待完成/停止确认。缺必需资源则拒绝整包更新。</x:v>
+        <x:v>普通反馈保留原最长5秒机制；序列等待每步所有循环/音频/震动完成，停顿后进下一步。保护打断/停止取消余下，未知先查询。</x:v>
       </x:c>
       <x:c r="H12" s="15"/>
       <x:c r="I12" s="15"/>
@@ -16210,7 +16209,7 @@
         <x:v>0：正常电量； 1：低电量</x:v>
       </x:c>
       <x:c r="D164" s="22" t="str">
-        <x:v>低电量时候通过一个事件来表达，动作列表增加一个动作。删掉</x:v>
+        <x:v>低电量时候通过一个事件来表达，动作规则增加一个动作。删掉</x:v>
       </x:c>
       <x:c r="E164" s="22"/>
       <x:c r="F164" s="22"/>
@@ -18351,15 +18350,15 @@
         <x:v>不能确定续航、充电时间和整机声学指标。</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" customHeight="1">
+    <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="20" t="str">
         <x:v>自定义动作控制链路</x:v>
       </x:c>
       <x:c r="B7" s="20" t="str">
-        <x:v>普通动作的App命令入口、0x05字节序、装机舵机安全范围、停止/完成通知未明确；0x51只用于舵机MCU OTA透传。</x:v>
+        <x:v>新增输入规则、单周期摇头/点头资源ID与标定、逐步/循环调度、完整规则原子启用/替换、能力/安全总时长、停止/完成与IMU互锁；0x51仍仅OTA透传。</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>自定义动作UI可以定义；实机预览、连续动作和中止须先补齐接口。</x:v>
+        <x:v>原13为3次复合点头不可代单次；23源Beta N待启用验收。四类可存草稿，能力未确认禁止真机启用。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
@@ -18978,7 +18977,7 @@
         <x:v>设备功能说明.md §1、§8.3；UAC234-A0-V1.2.pdf 第9页</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="15" t="str">
         <x:v>H05</x:v>
       </x:c>
@@ -18989,7 +18988,7 @@
         <x:v>实体按键 ×1</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>长按开关机，单击确认绑定，双击重启蓝牙；其他维护操作见固件需求。</x:v>
+        <x:v>长按开关机，单击确认启用，双击重启蓝牙；其他维护操作见固件需求。</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str"/>
       <x:c r="F10" s="15" t="str">
@@ -21674,7 +21673,7 @@
         <x:v>初次使用</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="167" customHeight="1">
+    <x:row r="9" ht="156" customHeight="1">
       <x:c r="A9" s="20" t="str">
         <x:v>initialization</x:v>
       </x:c>
@@ -21696,7 +21695,7 @@
 连接但未完成初始化继续使用初始行为表。
 失败保留当前设备状态；回执丢失先显示结果待确认并读回。
 已经初始化的设备进入原档案；缺完整 App 台账时仅展示设备摘要，不覆盖成长。
-原始模式即使有自定义绑定也无五行、无成长阶段；启用前先核对并保留这些已确认绑定。</x:v>
+原始模式即使有自定义绑定也无五行、无成长阶段；启用前先核对并保留这些已确认启用。</x:v>
       </x:c>
       <x:c r="F9" s="24" t="str">
         <x:v>初次使用</x:v>
@@ -21916,91 +21915,93 @@
         <x:v>成长</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="133" customHeight="1">
+    <x:row r="18" ht="156" customHeight="1">
       <x:c r="A18" s="15" t="str">
         <x:v>actions</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>动作列表</x:v>
+        <x:v>动作规则</x:v>
       </x:c>
       <x:c r="C18" s="22" t="str">
-        <x:v>作品名称、卡片次序、占用数量。
-草稿、资源已保存、绑定待同步、已绑定、结果待确认、待清理分别显示。
-作品当前绑定了哪些输入。</x:v>
+        <x:v>规则名称、输入事件、步骤摘要、已启用占用数。
+本机草稿、待启用、启用中、已启用、结果待确认、待清理分别显示。
+草稿版本与设备生效版本分开，标明输入能力是否已确认。</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>新建、编辑、预览、设置触发、取消绑定、删除。</x:v>
+        <x:v>新建、编辑、保存草稿、预览、启用、停用、删除。</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
-        <x:v>每设备最多 8 条已保存作品；App 草稿不占设备槽位。
-资源确认后占位；删除清理成功后才释放槽位。
-初始模式也可使用自定义动作，绑定不启用成长。
-编辑已绑定作品时使用新版本，旧版本持续生效至替换确认。
-8 条按已保存作品计，不按卡片数或绑定输入数计；待清理作品继续占位，清理完成才释放。</x:v>
+        <x:v>每设备最多8条已启用规则；本机草稿不占启用名额。
+一规则一输入；一个输入最多一条启用规则，冲突替换须确认。
+编辑已启用规则保留旧版，完整提交并读回后原子替换。
+初始模式可用动作规则，不因此启用成长。
+停用确认释放启用名额，资源清理状态独立；未知结果先核对。</x:v>
       </x:c>
       <x:c r="F18" s="23" t="str">
         <x:v>动作</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="218" customHeight="1">
+    <x:row r="19" ht="300" customHeight="1">
       <x:c r="A19" s="20" t="str">
         <x:v>action_editor</x:v>
       </x:c>
       <x:c r="B19" s="20" t="str">
-        <x:v>动作编辑</x:v>
+        <x:v>动作编排</x:v>
       </x:c>
       <x:c r="C19" s="20" t="str">
-        <x:v>名称：1–12 个可见字符。
-1–3 张已验证动作卡；每卡显示动作、已验证配套音频和震动设置。
-卡间停顿：0／0.5／1 秒；合计时长及 5 秒上限。</x:v>
+        <x:v>名称1–12个可见字符；一个输入事件。
+有序步骤：基础动作、重复次数、可选声音/震动、步间停顿。
+默认左右摇头5次→上下点头2次；显示2步、7个动作循环。
+建议1–10步、每步1–10次整数；总时长与能力状态分开显示。</x:v>
       </x:c>
       <x:c r="D19" s="20" t="str">
-        <x:v>添加、移除卡片，上下换序。
-选择配套音频或静音；选择已验证的震动档位或关闭。
-预览整个序列；停止；保存到设备。</x:v>
+        <x:v>选择输入；增加/删除/上下重排步骤；修改每步动作和次数。
+声音与震动默认关闭，只选已验证搭配；停顿0／0.5／1秒，末步不计。
+保存草稿（本机）；真机预览/停止；进入启用确认。</x:v>
       </x:c>
       <x:c r="E19" s="21" t="str">
-        <x:v>单卡时长取动作、音频、震动实际播放结束的最晚时间；总时长再加卡间停顿，最后一张无额外停顿。
-资源没有实测时长、配对或映射时不进入可用卡库。
-超 3 卡、名称无效、总时长超过 5 秒时不能保存到设备。
-仅编排已验证动作；不开放舵机角度、速度、限位或任意关键帧。
-离线允许保留 App 草稿；预览与设备保存需连接且鉴权成功。
-暗环境、深度睡眠、充电等不允许输出状态下拒绝预览；浅睡须先完成新增唤醒调度。
-预览不计成长、里程碑、故事；断连显示任务结果待确认，不假设设备已经停止。</x:v>
+        <x:v>步数与次数是本次设计建议，需研发容量/驱动确认，正式以设备能力为准。
+真实ID、角度、速度及周期时长待标定；不把原13复合点头作为单次。
+时长=max(周期×次数,音频跨度,震动跨度)逐步相加再加停顿；未知标待标定，禁止真机预览/启用。
+四类输入均可离线编辑并保存；23轻摇原Beta N，能力未确认时禁用真机启用。
+所有循环完成再下一步；声音/震动每步开始各一次，不随次数倍增。
+连接鉴权且状态允许才预览；停止取消余下，不续播。未知结果先查询。
+预览无成长；真实输入一次按原事件记录一次，光感无XP。
+显式保存草稿须输入/名称/至少一步/整数次数完整；不要求在线或资源已标定。未填完只算未保存编辑，不显示永久保存成功。</x:v>
       </x:c>
       <x:c r="F19" s="24" t="str">
         <x:v>动作</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="167" customHeight="1">
+    <x:row r="20" ht="156" customHeight="1">
       <x:c r="A20" s="15" t="str">
         <x:v>action_trigger</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>设置触发</x:v>
+        <x:v>输入与启用</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>当前已确认保存的作品版本。
-可绑定的普通轻触事件：1／4／7／10／13／16／19；显示来源表中的部位名称。
-每项现有绑定与本次待替换绑定。</x:v>
+        <x:v>触摸1／4／7／10／13／16／19、IMU轻摇23、唤醒28、光感变亮30。
+本规则所选的一个输入、设备支持状态、当前生效规则和待替换版本。
+23保留源Beta N，本轮新增实现；变暗29及保护/系统输入不开放。</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>选择一个或多个允许输入，确认绑定。
-已占用输入先确认替换；取消单个输入绑定。</x:v>
+        <x:v>选择一个输入；名称与步骤/次数完整后可保存本机草稿。
+启用前确认覆盖默认反馈；已占用时明确确认替换规则。
+完整校验、传输和提交后读回成功，显示已启用；可停用恢复默认。</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
-        <x:v>每输入最多一条作品，同一作品可绑定多个输入。
-资源未保存成功时不能绑定。
-绑定确认后，允许输出状态下该输入 100% 执行用户序列，不抽取成长反馈。
-输入仍受系统状态、保护与优先级限制；真人有效触摸仍按原事件计成长。
-取消绑定恢复当前生效基础表对应反馈，不删除作品或成长记录。
-提交回执缺失先读回，未知状态下不继续叠加写操作。</x:v>
+        <x:v>一规则一输入，一个输入最多一条启用规则。
+输入支持、基础动作、时长和调度未确认时可存草稿，不能启用。
+切换输入与编辑规则原子替换，确认前旧输入旧版仍生效。
+唤醒必要提示先执行；系统、保护、睡眠、静默、暗环境和充电限制始终优先。
+提交后未知先读回，阻止继续写；预览完成不等于已启用。</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
         <x:v>动作</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="201" customHeight="1">
+    <x:row r="21" ht="236" customHeight="1">
       <x:c r="A21" s="20" t="str">
         <x:v>device</x:v>
       </x:c>
@@ -22022,7 +22023,7 @@
 电量按设备的 0／25／50／75／100 档显示；无效值显示未知，不补成 0%。
 写入需回执确认；离线或回执未知不能显示保存成功。
 行为静默开启后不播放行为、不写事件，蓝牙控制保留；重启恢复关闭。
-重新开始养成需再次确认：清当前成长、里程碑、故事、绑定，回到无五行初始模式；作品保留为未绑定草稿。
+重新开始养成需再次确认：清当前成长、里程碑、故事、绑定，回到无五行初始模式；可编辑输入保留为未绑定草稿。
 源恢复出厂另有清事件、用户数据与重启语义，清理范围尚未完整明确；不能直接等同重新开始养成。</x:v>
       </x:c>
       <x:c r="F21" s="24" t="str">
@@ -22182,30 +22183,31 @@
       <x:c r="E31" s="15"/>
       <x:c r="F31" s="15"/>
     </x:row>
-    <x:row r="32" ht="116" customHeight="1">
+    <x:row r="32" ht="108" customHeight="1">
       <x:c r="A32" s="20" t="str">
-        <x:v>自定义动作保存与绑定</x:v>
+        <x:v>保存草稿与启用动作规则</x:v>
       </x:c>
       <x:c r="B32" s="20" t="str">
-        <x:v>动作列表 → 新建／编辑 → 选择 1–3 张已验证卡片
-调整次序、停顿、配套音频及震动 → 总时长校验 ≤5 秒
-允许状态下预览 → 收到完成／停止确认
-保存新资源版本 → 核对成功 → 设置触发
-选择事件 1／4／7／10／13／16／19 → 如占用则确认替换
-绑定版本读回一致 → 显示已绑定；原绑定在替换确认前持续生效</x:v>
+        <x:v>新建规则 → 选择一个输入（触摸／IMU轻摇／唤醒／变亮）
+编排左右摇头5次 → 上下点头2次；可增删重排和修改次数
+保存草稿到App本机（离线可用，不占设备槽位）
+连接鉴权 → 校验事件支持、基础动作、时长、完整资源和允许状态
+可预览整条一次 → 完成或停止确认；预览不计成长
+启用确认 → 冲突显式替换 → 完整规则传输/原子提交 → 读回一致后生效</x:v>
       </x:c>
       <x:c r="C32" s="20"/>
       <x:c r="D32" s="20"/>
       <x:c r="E32" s="20"/>
       <x:c r="F32" s="20"/>
     </x:row>
-    <x:row r="33" ht="48" customHeight="1">
+    <x:row r="33" ht="60" customHeight="1">
       <x:c r="A33" s="15" t="str">
-        <x:v>取消绑定与删除作品</x:v>
+        <x:v>停用与删除规则</x:v>
       </x:c>
       <x:c r="B33" s="15" t="str">
-        <x:v>取消绑定：选择一个输入 → 提交解绑 → 核对成功 → 恢复当前基础反馈
-删除作品：确认删除 → 解除全部引用 → 核对已无绑定 → 删除资源 → 核对清理完成 → 释放槽位</x:v>
+        <x:v>停用规则 → 设备读回成功 → 恢复当前基础反馈并释放启用名额，草稿保留
+删除已启用规则 → 先停用确认 → 清理设备资源 → 核对清理结果 → 删除作品
+纯本机草稿 → 本机删除，离线可用</x:v>
       </x:c>
       <x:c r="C33" s="15"/>
       <x:c r="D33" s="15"/>
@@ -25100,7 +25102,7 @@
       <x:c r="I27" s="20"/>
       <x:c r="J27" s="20"/>
     </x:row>
-    <x:row r="28" ht="48" customHeight="1">
+    <x:row r="28" ht="44" customHeight="1">
       <x:c r="A28" s="23" t="str">
         <x:v>成长与同步</x:v>
       </x:c>
@@ -25108,7 +25110,7 @@
         <x:v>自定义动作</x:v>
       </x:c>
       <x:c r="C28" s="15" t="str">
-        <x:v>普通轻触的用户绑定独立保存；生成新成长基础表后再覆盖有效用户绑定。阶段变化不删除作品或绑定。绑定事件由用户动作接管，不再参与该事件的成长反馈随机；物理输入仍按原输入事件计成长，App试玩不计。</x:v>
+        <x:v>用户规则独立保存，适用于获准触摸、轻摇23、唤醒28、变亮30；23须设备确认支持。生成成长基础表后保留已启用规则，阶段变化不删除。输出步骤和次数不改变真实事件count；光感与预览不计XP。</x:v>
       </x:c>
       <x:c r="D28" s="15"/>
       <x:c r="E28" s="15"/>
@@ -25190,7 +25192,7 @@
       <x:c r="I32" s="15"/>
       <x:c r="J32" s="15"/>
     </x:row>
-    <x:row r="33" ht="65" customHeight="1">
+    <x:row r="33" ht="76" customHeight="1">
       <x:c r="A33" s="24" t="str">
         <x:v>成长与同步</x:v>
       </x:c>
@@ -25198,7 +25200,7 @@
         <x:v>重新开始</x:v>
       </x:c>
       <x:c r="C33" s="20" t="str">
-        <x:v>重置养成需再次确认；恢复原始行为包并清当前成长摘要/台账、里程碑故事及用户触摸绑定，回到无五行、未初始化的原始模式，不运行五行情绪计算。用户动作作品可保留为未绑定草稿；重新启用从0 XP开始。该范围不同于源“恢复出厂清事件和用户数据后重启”，需要明确的重置养成业务接口，不能直接冒充已有恢复出厂语义。 原档案的缓存成长包和统计起点一并失效，不可用于新档案回滚。</x:v>
+        <x:v>重置养成需再次确认；恢复原始行为包并清当前成长摘要/台账、里程碑故事及用户输入规则，回到无五行、未初始化的原始模式，不运行五行情绪计算。用户动作可编辑输入可保留为未绑定草稿；重新启用从0 XP开始。该范围不同于源“恢复出厂清事件和用户数据后重启”，需要明确的重置养成业务接口，不能直接冒充已有恢复出厂语义。 原档案的缓存成长包和统计起点一并失效，不可用于新档案回滚。</x:v>
       </x:c>
       <x:c r="D33" s="20"/>
       <x:c r="E33" s="20"/>
@@ -25640,7 +25642,7 @@
       <x:c r="I57" s="20"/>
       <x:c r="J57" s="20"/>
     </x:row>
-    <x:row r="58" ht="48" customHeight="1">
+    <x:row r="58" ht="34" customHeight="1">
       <x:c r="A58" s="23" t="str">
         <x:v>反馈执行</x:v>
       </x:c>
@@ -25648,7 +25650,7 @@
         <x:v>通用规则</x:v>
       </x:c>
       <x:c r="C58" s="15" t="str">
-        <x:v>用户已确认绑定的普通轻触执行用户序列100%；保护与互斥优先。</x:v>
+        <x:v>用户已确认启用的普通轻触执行用户序列100%；保护与互斥优先。</x:v>
       </x:c>
       <x:c r="D58" s="15"/>
       <x:c r="E58" s="15"/>
